--- a/labeled/Add_Eating/July/multi_seed_results/seed_789/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_789/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,1162 +442,746 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>19.09892272949219</v>
+        <v>12.53672885894775</v>
       </c>
       <c r="B2" t="n">
-        <v>18.09631538391113</v>
+        <v>15.08974647521973</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10.77075099945068</v>
+        <v>13.33333301544189</v>
       </c>
       <c r="B3" t="n">
-        <v>11.42172908782959</v>
+        <v>19.56781768798828</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10.47992134094238</v>
+        <v>45</v>
       </c>
       <c r="B4" t="n">
-        <v>10.88748931884766</v>
+        <v>27.30671501159668</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20.37218475341797</v>
+        <v>28</v>
       </c>
       <c r="B5" t="n">
-        <v>17.3203182220459</v>
+        <v>46.44144821166992</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22.89999961853027</v>
+        <v>8.380952835083008</v>
       </c>
       <c r="B6" t="n">
-        <v>22.72365188598633</v>
+        <v>22.93880462646484</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>35.20000076293945</v>
+        <v>14.6245059967041</v>
       </c>
       <c r="B7" t="n">
-        <v>31.90952682495117</v>
+        <v>15.19820022583008</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32.41919708251953</v>
+        <v>25.5</v>
       </c>
       <c r="B8" t="n">
-        <v>32.60340881347656</v>
+        <v>26.94046401977539</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19.58863830566406</v>
+        <v>20.80867767333984</v>
       </c>
       <c r="B9" t="n">
-        <v>33.5204963684082</v>
+        <v>17.05184364318848</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>19.79999923706055</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="B10" t="n">
-        <v>17.21892929077148</v>
+        <v>28.21120834350586</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10.91269874572754</v>
+        <v>34.02777862548828</v>
       </c>
       <c r="B11" t="n">
-        <v>10.54410362243652</v>
+        <v>37.90696334838867</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>22.51984214782715</v>
+        <v>9.304603576660156</v>
       </c>
       <c r="B12" t="n">
-        <v>18.95217514038086</v>
+        <v>14.87711620330811</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80.69999694824219</v>
+        <v>21.13095283508301</v>
       </c>
       <c r="B13" t="n">
-        <v>78.3819580078125</v>
+        <v>21.85484886169434</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12.32741641998291</v>
+        <v>14.39764976501465</v>
       </c>
       <c r="B14" t="n">
-        <v>9.751444816589355</v>
+        <v>12.94018936157227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6.94444465637207</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B15" t="n">
-        <v>10.31259441375732</v>
+        <v>29.81779861450195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>8.630952835083008</v>
+        <v>11.4285717010498</v>
       </c>
       <c r="B16" t="n">
-        <v>11.21952056884766</v>
+        <v>15.76484870910645</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>26.44466209411621</v>
+        <v>19.5</v>
       </c>
       <c r="B17" t="n">
-        <v>23.48387718200684</v>
+        <v>21.20286560058594</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>30.66666603088379</v>
+        <v>51.59999847412109</v>
       </c>
       <c r="B18" t="n">
-        <v>27.24825668334961</v>
+        <v>34.29665756225586</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18.65079307556152</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="B19" t="n">
-        <v>14.54772472381592</v>
+        <v>23.50056457519531</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11.43984222412109</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="B20" t="n">
-        <v>10.70511722564697</v>
+        <v>14.96009254455566</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19.19686508178711</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n">
-        <v>16.67169380187988</v>
+        <v>24.39432907104492</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>30.55827713012695</v>
+        <v>19.39275169372559</v>
       </c>
       <c r="B22" t="n">
-        <v>26.31180953979492</v>
+        <v>21.98087692260742</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>69.90476226806641</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="B23" t="n">
-        <v>64.30117034912109</v>
+        <v>24.5703182220459</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>12.99603176116943</v>
+        <v>68.28571319580078</v>
       </c>
       <c r="B24" t="n">
-        <v>11.53709316253662</v>
+        <v>68.37400054931641</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27.32615089416504</v>
+        <v>33.5</v>
       </c>
       <c r="B25" t="n">
-        <v>23.56638145446777</v>
+        <v>33.15917587280273</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>87.80000305175781</v>
+        <v>7.737512111663818</v>
       </c>
       <c r="B26" t="n">
-        <v>85.76524353027344</v>
+        <v>10.5900297164917</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>46.20000076293945</v>
+        <v>12.5</v>
       </c>
       <c r="B27" t="n">
-        <v>41.80130386352539</v>
+        <v>14.1046085357666</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>17.53183174133301</v>
+        <v>13.22233104705811</v>
       </c>
       <c r="B28" t="n">
-        <v>10.19882965087891</v>
+        <v>14.203444480896</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31.80952453613281</v>
+        <v>20.66601371765137</v>
       </c>
       <c r="B29" t="n">
-        <v>25.48958015441895</v>
+        <v>22.33663749694824</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>85.69999694824219</v>
+        <v>24.87757110595703</v>
       </c>
       <c r="B30" t="n">
-        <v>80.5968017578125</v>
+        <v>24.70153427124023</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>23.5238094329834</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="B31" t="n">
-        <v>25.92349624633789</v>
+        <v>31.92507171630859</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12.5</v>
+        <v>11.2380952835083</v>
       </c>
       <c r="B32" t="n">
-        <v>10.87565612792969</v>
+        <v>29.10248756408691</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>15.0476188659668</v>
+        <v>48</v>
       </c>
       <c r="B33" t="n">
-        <v>15.04138469696045</v>
+        <v>42.07049560546875</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>27.18253898620605</v>
+        <v>50.40000152587891</v>
       </c>
       <c r="B34" t="n">
-        <v>16.77696418762207</v>
+        <v>43.58642578125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>81</v>
+        <v>39.5</v>
       </c>
       <c r="B35" t="n">
-        <v>75.3448486328125</v>
+        <v>36.31947708129883</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35.90000152587891</v>
+        <v>19.5</v>
       </c>
       <c r="B36" t="n">
-        <v>37.4977912902832</v>
+        <v>19.74215126037598</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36.23898315429688</v>
+        <v>9.402546882629395</v>
       </c>
       <c r="B37" t="n">
-        <v>28.04242706298828</v>
+        <v>21.65765953063965</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>79.36508178710938</v>
+        <v>7.783251285552979</v>
       </c>
       <c r="B38" t="n">
-        <v>80.35518646240234</v>
+        <v>10.55042362213135</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>26.09127044677734</v>
+        <v>26.15083312988281</v>
       </c>
       <c r="B39" t="n">
-        <v>18.00795555114746</v>
+        <v>28.73135375976562</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>58.76591491699219</v>
+        <v>19.79999923706055</v>
       </c>
       <c r="B40" t="n">
-        <v>29.28516578674316</v>
+        <v>21.70434761047363</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>30.09523773193359</v>
+        <v>59.40000152587891</v>
       </c>
       <c r="B41" t="n">
-        <v>22.3378963470459</v>
+        <v>59.158935546875</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>38.09523773193359</v>
+        <v>13.88888931274414</v>
       </c>
       <c r="B42" t="n">
-        <v>52.97008514404297</v>
+        <v>15.56123542785645</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>40.27777862548828</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="B43" t="n">
-        <v>22.08512496948242</v>
+        <v>45.62790679931641</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>34.70000076293945</v>
+        <v>20.53571510314941</v>
       </c>
       <c r="B44" t="n">
-        <v>23.92097854614258</v>
+        <v>17.47444915771484</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>61.90476226806641</v>
+        <v>25.39682579040527</v>
       </c>
       <c r="B45" t="n">
-        <v>55.93830871582031</v>
+        <v>25.55508613586426</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>59.70000076293945</v>
+        <v>24.50396919250488</v>
       </c>
       <c r="B46" t="n">
-        <v>36.11995697021484</v>
+        <v>29.98536491394043</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>40</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="B47" t="n">
-        <v>56.12373733520508</v>
+        <v>25.66572380065918</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>42.19047546386719</v>
+        <v>4.926108360290527</v>
       </c>
       <c r="B48" t="n">
-        <v>22.08254432678223</v>
+        <v>16.7942066192627</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>44.57143020629883</v>
+        <v>22.33104705810547</v>
       </c>
       <c r="B49" t="n">
-        <v>41.32494735717773</v>
+        <v>14.03549861907959</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>44.70000076293945</v>
+        <v>17.36111068725586</v>
       </c>
       <c r="B50" t="n">
-        <v>46.36714172363281</v>
+        <v>23.22218322753906</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>30.85210609436035</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="B51" t="n">
-        <v>26.99805641174316</v>
+        <v>22.87919044494629</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>58</v>
+        <v>31.84523773193359</v>
       </c>
       <c r="B52" t="n">
-        <v>54.08932113647461</v>
+        <v>31.54132270812988</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>17.10000038146973</v>
+        <v>40.09523773193359</v>
       </c>
       <c r="B53" t="n">
-        <v>13.54649829864502</v>
+        <v>34.84419250488281</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>21.5475025177002</v>
+        <v>19.64285659790039</v>
       </c>
       <c r="B54" t="n">
-        <v>19.94409561157227</v>
+        <v>14.19101619720459</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>38.09999847412109</v>
+        <v>12.69841289520264</v>
       </c>
       <c r="B55" t="n">
-        <v>35.84071731567383</v>
+        <v>10.59891033172607</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3.917727708816528</v>
+        <v>28.7952995300293</v>
       </c>
       <c r="B56" t="n">
-        <v>10.755446434021</v>
+        <v>35.20281600952148</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10.83743858337402</v>
+        <v>38.39373016357422</v>
       </c>
       <c r="B57" t="n">
-        <v>10.63646984100342</v>
+        <v>28.24660301208496</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>91.5</v>
+        <v>46.59999847412109</v>
       </c>
       <c r="B58" t="n">
-        <v>84.68115997314453</v>
+        <v>34.42138671875</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>16.38095283508301</v>
+        <v>57.20000076293945</v>
       </c>
       <c r="B59" t="n">
-        <v>28.26017379760742</v>
+        <v>30.82766342163086</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>18.51126289367676</v>
+        <v>27.18253898620605</v>
       </c>
       <c r="B60" t="n">
-        <v>15.59879875183105</v>
+        <v>23.25505638122559</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>6.502462863922119</v>
+        <v>73.40000152587891</v>
       </c>
       <c r="B61" t="n">
-        <v>4.377098560333252</v>
+        <v>77.02888488769531</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>39.68254089355469</v>
+        <v>37.21841430664062</v>
       </c>
       <c r="B62" t="n">
-        <v>40.08776092529297</v>
+        <v>38.28658294677734</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>40</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="B63" t="n">
-        <v>32.9627571105957</v>
+        <v>20.05320358276367</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>9.142857551574707</v>
+        <v>11.33333301544189</v>
       </c>
       <c r="B64" t="n">
-        <v>21.304931640625</v>
+        <v>10.5317440032959</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>13.80998992919922</v>
+        <v>22.5</v>
       </c>
       <c r="B65" t="n">
-        <v>14.22918033599854</v>
+        <v>12.95772743225098</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>57.14285659790039</v>
+        <v>11.56126499176025</v>
       </c>
       <c r="B66" t="n">
-        <v>66.4588623046875</v>
+        <v>17.10283660888672</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>29.10000038146973</v>
+        <v>24.38785552978516</v>
       </c>
       <c r="B67" t="n">
-        <v>25.38021659851074</v>
+        <v>25.96992301940918</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>78.35455322265625</v>
+        <v>10.7737512588501</v>
       </c>
       <c r="B68" t="n">
-        <v>76.60977172851562</v>
+        <v>9.305727958679199</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>19.5</v>
+        <v>32.41919708251953</v>
       </c>
       <c r="B69" t="n">
-        <v>14.10115528106689</v>
+        <v>29.89537239074707</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>24.10000038146973</v>
+        <v>30.55827713012695</v>
       </c>
       <c r="B70" t="n">
-        <v>24.9814567565918</v>
+        <v>28.56293106079102</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>25.46523094177246</v>
+        <v>41.20000076293945</v>
       </c>
       <c r="B71" t="n">
-        <v>23.75283622741699</v>
+        <v>37.65169525146484</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>40</v>
+        <v>45.52381134033203</v>
       </c>
       <c r="B72" t="n">
-        <v>53.42433166503906</v>
+        <v>41.71798324584961</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>31.84523773193359</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B73" t="n">
-        <v>26.27849006652832</v>
+        <v>16.99456405639648</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>69.63761138916016</v>
+        <v>60</v>
       </c>
       <c r="B74" t="n">
-        <v>63.28112030029297</v>
+        <v>45.1505126953125</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>18.31537628173828</v>
+        <v>34.37805938720703</v>
       </c>
       <c r="B75" t="n">
-        <v>16.69798469543457</v>
+        <v>36.59549331665039</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5.221674919128418</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="B76" t="n">
-        <v>7.028723239898682</v>
+        <v>19.55238914489746</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>60</v>
+        <v>10.24630546569824</v>
       </c>
       <c r="B77" t="n">
-        <v>69.42737579345703</v>
+        <v>18.02766227722168</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>54.90000152587891</v>
+        <v>44.46620941162109</v>
       </c>
       <c r="B78" t="n">
-        <v>57.13150405883789</v>
+        <v>36.13410949707031</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>68.85713958740234</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="B79" t="n">
-        <v>61.766845703125</v>
+        <v>14.61589336395264</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>80</v>
+        <v>13.80998992919922</v>
       </c>
       <c r="B80" t="n">
-        <v>76.326171875</v>
+        <v>19.76134490966797</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>8.380952835083008</v>
+        <v>19.84127044677734</v>
       </c>
       <c r="B81" t="n">
-        <v>34.34402465820312</v>
+        <v>24.33298110961914</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>14.6245059967041</v>
+        <v>8.275861740112305</v>
       </c>
       <c r="B82" t="n">
-        <v>20.79481887817383</v>
+        <v>37.8123893737793</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>14.20176315307617</v>
+        <v>28.40352630615234</v>
       </c>
       <c r="B83" t="n">
-        <v>17.06044578552246</v>
+        <v>25.83027458190918</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>87.80000305175781</v>
+        <v>59</v>
       </c>
       <c r="B84" t="n">
-        <v>85.76524353027344</v>
+        <v>51.96289825439453</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>11.4285717010498</v>
+        <v>11.50793647766113</v>
       </c>
       <c r="B85" t="n">
-        <v>13.55705738067627</v>
+        <v>16.51674270629883</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>25.95494651794434</v>
+        <v>46.70000076293945</v>
       </c>
       <c r="B86" t="n">
-        <v>23.60047149658203</v>
+        <v>30.3100700378418</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>8.380952835083008</v>
+        <v>31.63565063476562</v>
       </c>
       <c r="B87" t="n">
-        <v>34.34402465820312</v>
+        <v>29.31331825256348</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>12.30158710479736</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="B88" t="n">
-        <v>12.29853057861328</v>
+        <v>25.5164794921875</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4.926108360290527</v>
+        <v>59.70000076293945</v>
       </c>
       <c r="B89" t="n">
-        <v>9.289656639099121</v>
+        <v>45.35764694213867</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>68.28571319580078</v>
+        <v>23.11459350585938</v>
       </c>
       <c r="B90" t="n">
-        <v>58.76268768310547</v>
+        <v>27.7834587097168</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>13.51616096496582</v>
+        <v>24.68168449401855</v>
       </c>
       <c r="B91" t="n">
-        <v>13.50280952453613</v>
+        <v>22.18788528442383</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>53.20000076293945</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="B92" t="n">
-        <v>52.79479598999023</v>
+        <v>87.18818664550781</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.469147920608521</v>
+        <v>14.22924900054932</v>
       </c>
       <c r="B93" t="n">
-        <v>7.733145713806152</v>
+        <v>17.57712936401367</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>18.51126289367676</v>
+        <v>21.5475025177002</v>
       </c>
       <c r="B94" t="n">
-        <v>15.59879875183105</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>20.66601371765137</v>
-      </c>
-      <c r="B95" t="n">
-        <v>27.04792022705078</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>9.189723014831543</v>
-      </c>
-      <c r="B96" t="n">
-        <v>8.324490547180176</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>6.94444465637207</v>
-      </c>
-      <c r="B97" t="n">
-        <v>10.31259441375732</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>16.96428489685059</v>
-      </c>
-      <c r="B98" t="n">
-        <v>12.57577514648438</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="B99" t="n">
-        <v>36.61423492431641</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>9.402546882629395</v>
-      </c>
-      <c r="B100" t="n">
-        <v>13.83489418029785</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>7.783251285552979</v>
-      </c>
-      <c r="B101" t="n">
-        <v>7.435390949249268</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>99.20635223388672</v>
-      </c>
-      <c r="B102" t="n">
-        <v>97.94587707519531</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>34.02777862548828</v>
-      </c>
-      <c r="B103" t="n">
-        <v>29.0810375213623</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>39.17727661132812</v>
-      </c>
-      <c r="B104" t="n">
-        <v>39.14852905273438</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>25.79999923706055</v>
-      </c>
-      <c r="B105" t="n">
-        <v>28.86038017272949</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>25.39682579040527</v>
-      </c>
-      <c r="B106" t="n">
-        <v>11.19027519226074</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>26.10000038146973</v>
-      </c>
-      <c r="B107" t="n">
-        <v>23.52742958068848</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>17.36111068725586</v>
-      </c>
-      <c r="B108" t="n">
-        <v>24.25745582580566</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>31.84523773193359</v>
-      </c>
-      <c r="B109" t="n">
-        <v>26.27849006652832</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>19.64285659790039</v>
-      </c>
-      <c r="B110" t="n">
-        <v>17.67091941833496</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>12.69841289520264</v>
-      </c>
-      <c r="B111" t="n">
-        <v>9.488059997558594</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>38.39373016357422</v>
-      </c>
-      <c r="B112" t="n">
-        <v>37.55755233764648</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>46.59999847412109</v>
-      </c>
-      <c r="B113" t="n">
-        <v>36.2150764465332</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>15.51383399963379</v>
-      </c>
-      <c r="B114" t="n">
-        <v>14.68123912811279</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>73.40000152587891</v>
-      </c>
-      <c r="B115" t="n">
-        <v>68.82358551025391</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>33.79999923706055</v>
-      </c>
-      <c r="B116" t="n">
-        <v>32.94855880737305</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>13.29365062713623</v>
-      </c>
-      <c r="B117" t="n">
-        <v>7.632744789123535</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>11.56126499176025</v>
-      </c>
-      <c r="B118" t="n">
-        <v>22.72206687927246</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>45.52381134033203</v>
-      </c>
-      <c r="B119" t="n">
-        <v>37.57154083251953</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>79.36508178710938</v>
-      </c>
-      <c r="B120" t="n">
-        <v>73.50745391845703</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>10.7737512588501</v>
-      </c>
-      <c r="B121" t="n">
-        <v>9.031685829162598</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>58.76591491699219</v>
-      </c>
-      <c r="B122" t="n">
-        <v>65.92195129394531</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>32.41919708251953</v>
-      </c>
-      <c r="B123" t="n">
-        <v>32.60340881347656</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>25.5238094329834</v>
-      </c>
-      <c r="B124" t="n">
-        <v>25.65569114685059</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>39.17727661132812</v>
-      </c>
-      <c r="B125" t="n">
-        <v>42.42902374267578</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>30.19047546386719</v>
-      </c>
-      <c r="B126" t="n">
-        <v>29.52761459350586</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>11.4285717010498</v>
-      </c>
-      <c r="B127" t="n">
-        <v>13.55705738067627</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>97.94319152832031</v>
-      </c>
-      <c r="B128" t="n">
-        <v>90.37742614746094</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>16.5714282989502</v>
-      </c>
-      <c r="B129" t="n">
-        <v>15.5734691619873</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>60</v>
-      </c>
-      <c r="B130" t="n">
-        <v>57.99053192138672</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>80</v>
-      </c>
-      <c r="B131" t="n">
-        <v>76.21531677246094</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>103.8000030517578</v>
-      </c>
-      <c r="B132" t="n">
-        <v>99.71795654296875</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>38.19047546386719</v>
-      </c>
-      <c r="B133" t="n">
-        <v>29.02738189697266</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>44.46620941162109</v>
-      </c>
-      <c r="B134" t="n">
-        <v>33.14420700073242</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>46.70000076293945</v>
-      </c>
-      <c r="B135" t="n">
-        <v>34.26049041748047</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>19.84127044677734</v>
-      </c>
-      <c r="B136" t="n">
-        <v>16.33872604370117</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>28.40352630615234</v>
-      </c>
-      <c r="B137" t="n">
-        <v>25.42312049865723</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>13.88888931274414</v>
-      </c>
-      <c r="B138" t="n">
-        <v>13.70712089538574</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>80</v>
-      </c>
-      <c r="B139" t="n">
-        <v>77.64346313476562</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>12.74703598022461</v>
-      </c>
-      <c r="B140" t="n">
-        <v>12.55978107452393</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>26.09127044677734</v>
-      </c>
-      <c r="B141" t="n">
-        <v>18.00795555114746</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>33.90000152587891</v>
-      </c>
-      <c r="B142" t="n">
-        <v>21.13562202453613</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>14.6245059967041</v>
-      </c>
-      <c r="B143" t="n">
-        <v>20.79481887817383</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>85.69999694824219</v>
-      </c>
-      <c r="B144" t="n">
-        <v>80.5968017578125</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="B145" t="n">
-        <v>28.78817939758301</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>21.5475025177002</v>
-      </c>
-      <c r="B146" t="n">
-        <v>19.94828987121582</v>
+        <v>20.15134239196777</v>
       </c>
     </row>
   </sheetData>
